--- a/figure4/figure4B-C.Each_type_stimulation/plotting/data/Tarsal_candidate_stimulation.xlsx
+++ b/figure4/figure4B-C.Each_type_stimulation/plotting/data/Tarsal_candidate_stimulation.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>0Hz</t>
@@ -488,7 +493,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>a3</t>
+          <t>TPN1</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -498,37 +503,37 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1.495</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>10.385</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>12.495</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>14.83</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>17.29</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>a6</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -550,105 +555,105 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>a7</t>
+          <t>a6</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>9.06</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>10.87</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>13.755</v>
+        <v>0.055</v>
       </c>
       <c r="I4" t="n">
-        <v>14.425</v>
+        <v>0.34</v>
       </c>
       <c r="J4" t="n">
-        <v>16.245</v>
+        <v>0.445</v>
       </c>
       <c r="K4" t="n">
-        <v>17.455</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>18.635</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>a9</t>
+          <t>a7</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>9.06</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>10.87</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>13.755</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>14.425</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>16.245</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>17.455</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>18.635</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>TPN1</t>
+          <t>a9</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -658,31 +663,31 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.495</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>10.385</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>12.495</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>14.83</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>17.29</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>19.47</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
